--- a/artfynd/A 7074-2026 artfynd.xlsx
+++ b/artfynd/A 7074-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1746,6 +1746,1456 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131661959</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Båttjärnhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>461983</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7083177</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131661957</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Båttjärnhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>462047</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7083256</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131661960</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Båttjärnhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>461967</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7083178</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131661967</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Båttjärnhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>462178</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7083329</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131661965</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Båttjärnhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>462112</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7083314</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131661966</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Båttjärnhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>462142</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7083250</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 2,2 m upp i grantickerötad gran.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131661970</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Båttjärnhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>462070</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7083064</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131661956</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Båttjärnhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>462182</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7083361</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131661968</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57077</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Båttjärnhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>461956</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7083218</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Flög precis förbi ansiktet och landade några meter ifrån mig och lade sig och tryckte</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131661961</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Båttjärnhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>462022</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7083014</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131661962</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Båttjärnhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>462044</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7083051</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131661964</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Båttjärnhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>462041</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7083052</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131661969</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91824</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Båttjärnhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>462054</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7083316</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131661958</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Båttjärnhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>462032</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7083180</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7074-2026 artfynd.xlsx
+++ b/artfynd/A 7074-2026 artfynd.xlsx
@@ -2796,7 +2796,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131661962</v>
+        <v>131661964</v>
       </c>
       <c r="B21" t="n">
         <v>57898</v>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462044</v>
+        <v>462041</v>
       </c>
       <c r="R21" t="n">
-        <v>7083051</v>
+        <v>7083052</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2898,7 +2898,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131661964</v>
+        <v>131661962</v>
       </c>
       <c r="B22" t="n">
         <v>57898</v>
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462041</v>
+        <v>462044</v>
       </c>
       <c r="R22" t="n">
-        <v>7083052</v>
+        <v>7083051</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 7074-2026 artfynd.xlsx
+++ b/artfynd/A 7074-2026 artfynd.xlsx
@@ -1752,7 +1752,7 @@
         <v>131661959</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>131661957</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>131661960</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>131661967</v>
       </c>
       <c r="B14" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>131661965</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>131661966</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>131661970</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>131661956</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>131661968</v>
       </c>
       <c r="B19" t="n">
-        <v>57077</v>
+        <v>57078</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>131661961</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>131661964</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>131661962</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>131661969</v>
       </c>
       <c r="B23" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>131661958</v>
       </c>
       <c r="B24" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 7074-2026 artfynd.xlsx
+++ b/artfynd/A 7074-2026 artfynd.xlsx
@@ -1752,7 +1752,7 @@
         <v>131661959</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>131661957</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>131661960</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>131661967</v>
       </c>
       <c r="B14" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>131661965</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>131661966</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>131661970</v>
       </c>
       <c r="B17" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>131661956</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>131661968</v>
       </c>
       <c r="B19" t="n">
-        <v>57078</v>
+        <v>57081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>131661961</v>
       </c>
       <c r="B20" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>131661964</v>
       </c>
       <c r="B21" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>131661962</v>
       </c>
       <c r="B22" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>131661969</v>
       </c>
       <c r="B23" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>131661958</v>
       </c>
       <c r="B24" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 7074-2026 artfynd.xlsx
+++ b/artfynd/A 7074-2026 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62055345</v>
+        <v>89596509</v>
       </c>
       <c r="B2" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Båttjärnhögarna - Nytjärnberget - Hömyrhöjden, Jmt</t>
+          <t>Båttjärnhögarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462129.9189089586</v>
+        <v>462107</v>
       </c>
       <c r="R2" t="n">
-        <v>7083319.391111039</v>
+        <v>7083361</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1998-08-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1998-08-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På minst fem sälgar inom ca 3 ha, bl.a. 8 resp. 7 ex. 1992?: Funnen på en sälg 1998: Steget Före. Inventering av Sv. Ticksällskapet 1996 i delar av området. Området krymper årligen genom nya avverkningar. Västra Båttjärnhögens östsluttning, ca 600 m SSV om Stortjärns sydspets,</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,89 +756,65 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Lst Z Artdatabas</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62055342</v>
+        <v>62055345</v>
       </c>
       <c r="B3" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Båttjärnhögarna - Nytjärnberget - Hömyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462129.9189089586</v>
+        <v>462130</v>
       </c>
       <c r="R3" t="n">
-        <v>7083319.391111039</v>
+        <v>7083319</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -888,24 +844,14 @@
           <t>1998-08-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1998-08-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Tre ex på en asp. 1998: Steget Före. Inventering av Sv. Ticksällskapet 1996 i delar av området. Området krymper årligen genom nya avverkningar. Västra Båttjärnhögens östsluttning, ca 600 m SSV om Stortjärns sydspets,</t>
+          <t>På minst fem sälgar inom ca 3 ha, bl.a. 8 resp. 7 ex. 1992?: Funnen på en sälg 1998: Steget Före. Inventering av Sv. Ticksällskapet 1996 i delar av området. Området krymper årligen genom nya avverkningar. Västra Båttjärnhögens östsluttning, ca 600 m SSV om Stortjärns sydspets,</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,12 +865,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -946,53 +892,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89596490</v>
+        <v>120851930</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Båttjärnhögarna, Jmt</t>
+          <t>Båttjärnhögarna, mellan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462067.8206695397</v>
+        <v>462113</v>
       </c>
       <c r="R4" t="n">
-        <v>7083184.810089602</v>
+        <v>7083264</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,22 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1992-07-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1992-07-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,31 +977,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Staffan Åström, Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89596528</v>
+        <v>89596529</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1102,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461989.8752936311</v>
+        <v>462196</v>
       </c>
       <c r="R5" t="n">
-        <v>7083127.123205063</v>
+        <v>7083228</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,19 +1057,9 @@
           <t>2020-09-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,15 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89596529</v>
+        <v>131661969</v>
       </c>
       <c r="B6" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462195.9050463758</v>
+        <v>462054</v>
       </c>
       <c r="R6" t="n">
-        <v>7083227.786481529</v>
+        <v>7083316</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,22 +1155,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,31 +1175,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89596525</v>
+        <v>89596490</v>
       </c>
       <c r="B7" t="n">
-        <v>56278</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,21 +1198,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100011</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1334,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462191.0769391584</v>
+        <v>462068</v>
       </c>
       <c r="R7" t="n">
-        <v>7083230.048817792</v>
+        <v>7083185</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,19 +1255,9 @@
           <t>2020-09-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,15 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89596516</v>
+        <v>62055342</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,37 +1299,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Båttjärnhögarna, Jmt</t>
+          <t>Båttjärnhögarna - Nytjärnberget - Hömyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462097.9334425154</v>
+        <v>462130</v>
       </c>
       <c r="R8" t="n">
-        <v>7083411.905695659</v>
+        <v>7083319</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1480,22 +1362,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-08-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-08-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Tre ex på en asp. 1998: Steget Före. Inventering av Sv. Ticksällskapet 1996 i delar av området. Området krymper årligen genom nya avverkningar. Västra Båttjärnhögens östsluttning, ca 600 m SSV om Stortjärns sydspets,</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,6 +1383,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -1515,53 +1397,48 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Bengt Petterson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Lst Z Artdatabas</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89596509</v>
+        <v>89596528</v>
       </c>
       <c r="B9" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1571,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462107.0296075577</v>
+        <v>461990</v>
       </c>
       <c r="R9" t="n">
-        <v>7083361.103602947</v>
+        <v>7083127</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,19 +1481,9 @@
           <t>2020-09-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,15 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120851930</v>
+        <v>131661970</v>
       </c>
       <c r="B10" t="n">
-        <v>91259</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,37 +1525,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Båttjärnhögarna, mellan, Jmt</t>
+          <t>Båttjärnhögarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462113</v>
+        <v>462070</v>
       </c>
       <c r="R10" t="n">
-        <v>7083264</v>
+        <v>7083064</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1717,12 +1579,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1992-07-08</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1992-07-08</t>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,44 +1604,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Staffan Åström, Bengt Petterson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131661959</v>
+        <v>89596516</v>
       </c>
       <c r="B11" t="n">
-        <v>57948</v>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1784,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461983</v>
+        <v>462098</v>
       </c>
       <c r="R11" t="n">
-        <v>7083177</v>
+        <v>7083412</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1814,17 +1681,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,26 +1697,35 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131661957</v>
+        <v>89596525</v>
       </c>
       <c r="B12" t="n">
-        <v>57948</v>
+        <v>57864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,16 +1733,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100011</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1886,10 +1757,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462047</v>
+        <v>462191</v>
       </c>
       <c r="R12" t="n">
-        <v>7083256</v>
+        <v>7083230</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,17 +1787,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska och äldre</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,22 +1807,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131661960</v>
+        <v>131661956</v>
       </c>
       <c r="B13" t="n">
-        <v>57948</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1988,10 +1858,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461967</v>
+        <v>462182</v>
       </c>
       <c r="R13" t="n">
-        <v>7083178</v>
+        <v>7083361</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +1925,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131661967</v>
+        <v>131661957</v>
       </c>
       <c r="B14" t="n">
-        <v>58107</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,46 +1936,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Båttjärnhögarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462178</v>
+        <v>462047</v>
       </c>
       <c r="R14" t="n">
-        <v>7083329</v>
+        <v>7083256</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,6 +1996,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131661965</v>
+        <v>131661958</v>
       </c>
       <c r="B15" t="n">
-        <v>57948</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,10 +2062,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462112</v>
+        <v>462032</v>
       </c>
       <c r="R15" t="n">
-        <v>7083314</v>
+        <v>7083180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,7 +2102,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131661966</v>
+        <v>131661959</v>
       </c>
       <c r="B16" t="n">
-        <v>57948</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,24 +2158,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Båttjärnhögarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462142</v>
+        <v>461983</v>
       </c>
       <c r="R16" t="n">
-        <v>7083250</v>
+        <v>7083177</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2349,7 +2204,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gammalt bohål ca 2,2 m upp i grantickerötad gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,10 +2231,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131661970</v>
+        <v>131661960</v>
       </c>
       <c r="B17" t="n">
-        <v>79315</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,21 +2242,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2411,10 +2266,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462070</v>
+        <v>461967</v>
       </c>
       <c r="R17" t="n">
-        <v>7083064</v>
+        <v>7083178</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2306,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,10 +2333,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131661956</v>
+        <v>131661961</v>
       </c>
       <c r="B18" t="n">
-        <v>57948</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2513,10 +2368,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462182</v>
+        <v>462022</v>
       </c>
       <c r="R18" t="n">
-        <v>7083361</v>
+        <v>7083014</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,7 +2408,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2580,10 +2435,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131661968</v>
+        <v>131661962</v>
       </c>
       <c r="B19" t="n">
-        <v>57127</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,16 +2446,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2608,29 +2463,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Båttjärnhögarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461956</v>
+        <v>462044</v>
       </c>
       <c r="R19" t="n">
-        <v>7083218</v>
+        <v>7083051</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,7 +2510,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Flög precis förbi ansiktet och landade några meter ifrån mig och lade sig och tryckte</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131661961</v>
+        <v>131661964</v>
       </c>
       <c r="B20" t="n">
-        <v>57948</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462022</v>
+        <v>462041</v>
       </c>
       <c r="R20" t="n">
-        <v>7083014</v>
+        <v>7083052</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2769,7 +2612,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,10 +2639,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131661962</v>
+        <v>131661965</v>
       </c>
       <c r="B21" t="n">
-        <v>57948</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2831,10 +2674,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462044</v>
+        <v>462112</v>
       </c>
       <c r="R21" t="n">
-        <v>7083051</v>
+        <v>7083314</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2871,7 +2714,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2898,10 +2741,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131661964</v>
+        <v>131661966</v>
       </c>
       <c r="B22" t="n">
-        <v>57948</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,16 +2770,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Båttjärnhögarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462041</v>
+        <v>462142</v>
       </c>
       <c r="R22" t="n">
-        <v>7083052</v>
+        <v>7083250</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2973,7 +2824,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gammalt bohål ca 2,2 m upp i grantickerötad gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,45 +2851,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131661969</v>
+        <v>131661968</v>
       </c>
       <c r="B23" t="n">
-        <v>91885</v>
+        <v>57153</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Båttjärnhögarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462054</v>
+        <v>461956</v>
       </c>
       <c r="R23" t="n">
-        <v>7083316</v>
+        <v>7083218</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3071,6 +2934,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flög precis förbi ansiktet och landade några meter ifrån mig och lade sig och tryckte</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3097,10 +2965,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131661958</v>
+        <v>131661967</v>
       </c>
       <c r="B24" t="n">
-        <v>57948</v>
+        <v>58136</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3108,34 +2976,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Båttjärnhögarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462032</v>
+        <v>462178</v>
       </c>
       <c r="R24" t="n">
-        <v>7083180</v>
+        <v>7083329</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3168,11 +3048,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 7074-2026 artfynd.xlsx
+++ b/artfynd/A 7074-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596509</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055345</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120851930</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596529</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661969</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596490</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055342</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596528</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661970</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1719,6 +1769,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596516</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1820,6 +1875,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596525</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1922,6 +1982,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661956</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2024,6 +2089,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661957</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2126,6 +2196,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661958</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2228,6 +2303,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661959</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2330,6 +2410,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661960</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2432,6 +2517,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661961</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2534,6 +2624,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661962</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2636,6 +2731,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661964</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2738,6 +2838,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661965</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2848,6 +2953,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661966</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2962,6 +3072,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661968</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3071,8 +3186,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131661967</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>